--- a/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-human-oversight.xlsx
+++ b/r5-aist-trustworthyai-poc-pipeline/StructureDefinition-eu-ai-human-oversight.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>EU AI Act Human Oversight (HL)</t>
+    <t>EU AI Human Oversight Assessment</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T09:07:35+00:00</t>
+    <t>2026-06-18T11:52:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Documents the professional review and clinical decision-making regarding AI outputs.</t>
+    <t>An ArtifactAssessment profile documenting professional review of an AI-generated output, including whether the result was accepted, corrected, modified, or overridden.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -526,7 +526,7 @@
 </t>
   </si>
   <si>
-    <t>Date last changed</t>
+    <t>Date and time of human oversight assessment</t>
   </si>
   <si>
     <t>The date  (and optionally time) when the artifact assessment was published. The date must change when the disposition changes and it must change if the workflow status code changes. In addition, it should change when the substantive content of the artifact assessment changes.</t>
@@ -2757,7 +2757,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>159</v>
       </c>
@@ -2770,13 +2770,13 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>83</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>18</v>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="G25" t="s" s="2">
         <v>83</v>
@@ -4729,7 +4729,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>247</v>
       </c>
@@ -4750,7 +4750,7 @@
         <v>83</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>18</v>
@@ -5395,7 +5395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>280</v>
       </c>
@@ -5414,7 +5414,7 @@
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>18</v>
